--- a/RAG/data/Categorized_Locations.xlsx
+++ b/RAG/data/Categorized_Locations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EGYReal\RAG\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B730EA3E-DA3B-4EF7-93E6-6E344F61FAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7E6B62-61C4-420B-B5B7-3F919DDE28D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
